--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,242 +417,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -741,13 +729,13 @@
         <v>250</v>
       </c>
       <c r="T2" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="U2" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="V2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
@@ -756,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -765,31 +753,31 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="AE2" t="n">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="AF2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AG2" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="AH2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -801,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AQ2" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="AR2" t="n">
         <v>364</v>
@@ -1057,10 +1045,10 @@
         <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="U4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1069,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1081,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1090,13 +1078,13 @@
         <v>429</v>
       </c>
       <c r="AE4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AF4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AG4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1105,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1117,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1126,7 +1114,7 @@
         <v>429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AR4" t="n">
         <v>363</v>
@@ -1218,7 +1206,7 @@
         <v>219</v>
       </c>
       <c r="U5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1239,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>425</v>
@@ -1254,7 +1242,7 @@
         <v>219</v>
       </c>
       <c r="AG5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1275,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
         <v>425</v>
@@ -1373,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="U6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1397,28 +1385,28 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AE6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AF6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1433,16 +1421,16 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AR6" t="n">
         <v>354</v>
@@ -1531,13 +1519,13 @@
         <v>66.67</v>
       </c>
       <c r="T7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="U7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1561,19 +1549,19 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AE7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AF7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1597,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AQ7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AR7" t="n">
         <v>336</v>
@@ -1689,16 +1677,16 @@
         <v>120</v>
       </c>
       <c r="T8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="U8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1719,22 +1707,22 @@
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AE8" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="AF8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="AG8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1755,10 +1743,10 @@
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AQ8" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AR8" t="n">
         <v>304</v>
@@ -1847,13 +1835,13 @@
         <v>33.33</v>
       </c>
       <c r="T9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="U9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1877,19 +1865,19 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AE9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AF9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AG9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1913,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AQ9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AR9" t="n">
         <v>288</v>
@@ -2008,16 +1996,16 @@
         <v>186</v>
       </c>
       <c r="U10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>7</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -2044,16 +2032,16 @@
         <v>186</v>
       </c>
       <c r="AG10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -2163,19 +2151,19 @@
         <v>75</v>
       </c>
       <c r="T11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="U11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2187,31 +2175,31 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>407</v>
       </c>
       <c r="AE11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AF11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AG11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2223,16 +2211,16 @@
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
         <v>407</v>
       </c>
       <c r="AQ11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AR11" t="n">
         <v>373</v>
@@ -2321,13 +2309,13 @@
         <v>256.15</v>
       </c>
       <c r="T12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
@@ -2345,25 +2333,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AE12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AF12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>1</v>
@@ -2381,16 +2369,16 @@
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AQ12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AR12" t="n">
         <v>383</v>
@@ -2479,13 +2467,13 @@
         <v>533.3299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="U13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2509,19 +2497,19 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AE13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AF13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2545,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AQ13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AR13" t="n">
         <v>373</v>
@@ -2637,16 +2625,16 @@
         <v>30.14</v>
       </c>
       <c r="T14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="U14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2670,19 +2658,19 @@
         <v>426</v>
       </c>
       <c r="AE14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AF14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AH14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2706,7 +2694,7 @@
         <v>426</v>
       </c>
       <c r="AQ14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AR14" t="n">
         <v>364</v>
@@ -2795,13 +2783,13 @@
         <v>31.25</v>
       </c>
       <c r="T15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="U15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
@@ -2819,25 +2807,25 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AE15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AF15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AG15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
         <v>1</v>
@@ -2855,16 +2843,16 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AR15" t="n">
         <v>324</v>
@@ -2953,13 +2941,13 @@
         <v>59.86</v>
       </c>
       <c r="T16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2968,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2980,22 +2968,22 @@
         <v>30</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AE16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AF16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3004,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3016,13 +3004,13 @@
         <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AQ16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AR16" t="n">
         <v>288</v>
@@ -3111,25 +3099,25 @@
         <v>259.09</v>
       </c>
       <c r="T17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="U17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3141,31 +3129,31 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AE17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AF17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -3177,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AQ17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AR17" t="n">
         <v>370</v>
@@ -3269,19 +3257,19 @@
         <v>383.33</v>
       </c>
       <c r="T18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="U18" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="V18" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="W18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3299,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AE18" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="AF18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AG18" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="AH18" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3335,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ18" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AR18" t="n">
         <v>366</v>
@@ -3427,13 +3415,13 @@
         <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="V19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3460,16 +3448,16 @@
         <v>454</v>
       </c>
       <c r="AE19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AF19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3496,7 +3484,7 @@
         <v>454</v>
       </c>
       <c r="AQ19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AR19" t="n">
         <v>423</v>
@@ -3746,10 +3734,10 @@
         <v>186</v>
       </c>
       <c r="U21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>2</v>
@@ -3767,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3782,10 +3770,10 @@
         <v>186</v>
       </c>
       <c r="AG21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>2</v>
@@ -3803,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -3901,16 +3889,16 @@
         <v>87.18000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="U22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X22" t="n">
         <v>7</v>
@@ -3931,22 +3919,22 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AE22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AF22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AJ22" t="n">
         <v>7</v>
@@ -3967,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AQ22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AR22" t="n">
         <v>410</v>
@@ -4059,19 +4047,19 @@
         <v>133.33</v>
       </c>
       <c r="T23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="U23" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -4089,25 +4077,25 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AE23" t="n">
+        <v>313</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG23" t="n">
         <v>296</v>
       </c>
-      <c r="AF23" t="n">
-        <v>236</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>286</v>
-      </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -4125,10 +4113,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AQ23" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="AR23" t="n">
         <v>450</v>
@@ -4217,22 +4205,22 @@
         <v>78.33</v>
       </c>
       <c r="T24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -4241,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4250,25 +4238,25 @@
         <v>402</v>
       </c>
       <c r="AE24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AH24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4277,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -4286,7 +4274,7 @@
         <v>402</v>
       </c>
       <c r="AQ24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AR24" t="n">
         <v>359</v>
@@ -4375,13 +4363,13 @@
         <v>45.19</v>
       </c>
       <c r="T25" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="U25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4405,19 +4393,19 @@
         <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AE25" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="AF25" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AG25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4441,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AQ25" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AR25" t="n">
         <v>308</v>
@@ -4533,25 +4521,25 @@
         <v>170</v>
       </c>
       <c r="T26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="U26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V26" t="n">
+        <v>18</v>
+      </c>
+      <c r="W26" t="n">
+        <v>20</v>
+      </c>
+      <c r="X26" t="n">
         <v>7</v>
       </c>
-      <c r="W26" t="n">
-        <v>19</v>
-      </c>
-      <c r="X26" t="n">
-        <v>11</v>
-      </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4566,28 +4554,28 @@
         <v>472</v>
       </c>
       <c r="AE26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AF26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AH26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>7</v>
       </c>
-      <c r="AI26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>11</v>
-      </c>
       <c r="AK26" t="n">
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
@@ -4602,7 +4590,7 @@
         <v>472</v>
       </c>
       <c r="AQ26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AR26" t="n">
         <v>419</v>
@@ -4691,13 +4679,13 @@
         <v>43.2</v>
       </c>
       <c r="T27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="U27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4721,19 +4709,19 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AE27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AF27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="AG27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4757,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AQ27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AR27" t="n">
         <v>342</v>
@@ -4849,19 +4837,19 @@
         <v>42.86</v>
       </c>
       <c r="T28" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="U28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4873,31 +4861,31 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AE28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AF28" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4909,16 +4897,16 @@
         <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AQ28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AR28" t="n">
         <v>384</v>
@@ -5007,13 +4995,13 @@
         <v>120</v>
       </c>
       <c r="T29" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="U29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5031,25 +5019,25 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AE29" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AF29" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AG29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -5067,16 +5055,16 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AQ29" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AR29" t="n">
         <v>357</v>
@@ -5165,22 +5153,22 @@
         <v>458.57</v>
       </c>
       <c r="T30" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="U30" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -5189,34 +5177,34 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="AE30" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="AF30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5231,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AQ30" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AR30" t="n">
         <v>457</v>
@@ -5326,13 +5314,13 @@
         <v>8</v>
       </c>
       <c r="U31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="V31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -5356,19 +5344,19 @@
         <v>332</v>
       </c>
       <c r="AE31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AF31" t="n">
         <v>8</v>
       </c>
       <c r="AG31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AI31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
@@ -5392,7 +5380,7 @@
         <v>332</v>
       </c>
       <c r="AQ31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AR31" t="n">
         <v>315</v>
@@ -5481,19 +5469,19 @@
         <v>164.29</v>
       </c>
       <c r="T32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="U32" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="V32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -5505,31 +5493,31 @@
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AC32" t="n">
         <v>3</v>
       </c>
       <c r="AD32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AE32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AF32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="AH32" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5541,16 +5529,16 @@
         <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AO32" t="n">
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AR32" t="n">
         <v>308</v>
@@ -5639,19 +5627,19 @@
         <v>97.65000000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="U33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -5663,31 +5651,31 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AE33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AF33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="AH33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AJ33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5699,16 +5687,16 @@
         <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AQ33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AR33" t="n">
         <v>365</v>
@@ -5797,16 +5785,16 @@
         <v>88.89</v>
       </c>
       <c r="T34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="U34" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -5821,28 +5809,28 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AE34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AF34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="AH34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -5857,16 +5845,16 @@
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AQ34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AR34" t="n">
         <v>410</v>
@@ -5955,13 +5943,13 @@
         <v>156.06</v>
       </c>
       <c r="T35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="U35" t="n">
         <v>182</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5985,19 +5973,19 @@
         <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AE35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AF35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="n">
         <v>182</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -6021,10 +6009,10 @@
         <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AR35" t="n">
         <v>303</v>
@@ -6113,13 +6101,13 @@
         <v>24</v>
       </c>
       <c r="T36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="U36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="V36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6143,19 +6131,19 @@
         <v>7</v>
       </c>
       <c r="AD36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AE36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AF36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="AH36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6179,10 +6167,10 @@
         <v>7</v>
       </c>
       <c r="AP36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AR36" t="n">
         <v>412</v>
@@ -6271,16 +6259,16 @@
         <v>160</v>
       </c>
       <c r="T37" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="U37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -6295,28 +6283,28 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AE37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AF37" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AG37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="AH37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -6331,16 +6319,16 @@
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AQ37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AR37" t="n">
         <v>371</v>
@@ -6429,19 +6417,19 @@
         <v>183.33</v>
       </c>
       <c r="T38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="U38" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="V38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -6459,25 +6447,25 @@
         <v>4</v>
       </c>
       <c r="AD38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AE38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AF38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AG38" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="AH38" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
         <v>2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -6495,10 +6483,10 @@
         <v>4</v>
       </c>
       <c r="AP38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AQ38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AR38" t="n">
         <v>453</v>
@@ -6587,22 +6575,22 @@
         <v>189.29</v>
       </c>
       <c r="T39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="U39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="W39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
@@ -6620,25 +6608,25 @@
         <v>474</v>
       </c>
       <c r="AE39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AF39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AI39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AK39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>1</v>
@@ -6656,7 +6644,7 @@
         <v>474</v>
       </c>
       <c r="AQ39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AR39" t="n">
         <v>445</v>
@@ -6745,19 +6733,19 @@
         <v>137.5</v>
       </c>
       <c r="T40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="U40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="V40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -6775,25 +6763,25 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AE40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AF40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AG40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="AH40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6811,10 +6799,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AR40" t="n">
         <v>379</v>
@@ -6903,13 +6891,13 @@
         <v>240</v>
       </c>
       <c r="T41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="U41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="V41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -6933,19 +6921,19 @@
         <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AE41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AF41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AG41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AH41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -6969,10 +6957,10 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AR41" t="n">
         <v>335</v>
@@ -7061,16 +7049,16 @@
         <v>75</v>
       </c>
       <c r="T42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="U42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -7085,28 +7073,28 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AE42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AF42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AH42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AJ42" t="n">
         <v>0</v>
@@ -7121,16 +7109,16 @@
         <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AR42" t="n">
         <v>371</v>
@@ -7219,19 +7207,19 @@
         <v>233.33</v>
       </c>
       <c r="T43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="U43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -7249,25 +7237,25 @@
         <v>1</v>
       </c>
       <c r="AD43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AE43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AF43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AG43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AH43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -7285,10 +7273,10 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AQ43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AR43" t="n">
         <v>331</v>
@@ -7377,19 +7365,19 @@
         <v>82.94</v>
       </c>
       <c r="T44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="U44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="V44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -7407,25 +7395,25 @@
         <v>3</v>
       </c>
       <c r="AD44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AE44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AF44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AG44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="AH44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -7443,10 +7431,10 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AQ44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AR44" t="n">
         <v>301</v>
@@ -7535,16 +7523,16 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="U45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="V45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="X45" t="n">
         <v>87</v>
@@ -7565,22 +7553,22 @@
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="AE45" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AF45" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="AG45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AI45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
@@ -7601,10 +7589,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AQ45" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AR45" t="n">
         <v>355</v>
@@ -7693,13 +7681,13 @@
         <v>209.53</v>
       </c>
       <c r="T46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="U46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="W46" t="n">
         <v>2</v>
@@ -7717,25 +7705,25 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC46" t="n">
         <v>6</v>
       </c>
       <c r="AD46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AE46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AF46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AI46" t="n">
         <v>2</v>
@@ -7753,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO46" t="n">
         <v>6</v>
       </c>
       <c r="AP46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AR46" t="n">
         <v>434</v>
@@ -7854,13 +7842,13 @@
         <v>170</v>
       </c>
       <c r="U47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -7875,28 +7863,28 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AE47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AF47" t="n">
         <v>170</v>
       </c>
       <c r="AG47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="n">
         <v>0</v>
@@ -7911,16 +7899,16 @@
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AQ47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AR47" t="n">
         <v>375</v>
@@ -8009,19 +7997,19 @@
         <v>65</v>
       </c>
       <c r="T48" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="U48" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="V48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -8033,31 +8021,31 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>414</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>213</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>134</v>
+      </c>
+      <c r="AH48" t="n">
         <v>24</v>
       </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>413</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>192</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>220</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>145</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>22</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -8069,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ48" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AR48" t="n">
         <v>363</v>
@@ -8170,7 +8158,7 @@
         <v>211</v>
       </c>
       <c r="U49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -8179,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -8191,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8206,10 +8194,10 @@
         <v>211</v>
       </c>
       <c r="AG49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AH49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -8227,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -8325,19 +8313,19 @@
         <v>283.33</v>
       </c>
       <c r="T50" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U50" t="n">
         <v>192</v>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -8349,7 +8337,7 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AC50" t="n">
         <v>2</v>
@@ -8358,22 +8346,22 @@
         <v>450</v>
       </c>
       <c r="AE50" t="n">
+        <v>226</v>
+      </c>
+      <c r="AF50" t="n">
         <v>224</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>226</v>
       </c>
       <c r="AG50" t="n">
         <v>192</v>
       </c>
       <c r="AH50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -8385,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO50" t="n">
         <v>2</v>
@@ -8394,7 +8382,7 @@
         <v>450</v>
       </c>
       <c r="AQ50" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AR50" t="n">
         <v>372</v>
@@ -8483,19 +8471,19 @@
         <v>275</v>
       </c>
       <c r="T51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="U51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="V51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -8507,31 +8495,31 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AE51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AF51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AG51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="AH51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AI51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
@@ -8543,16 +8531,16 @@
         <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AQ51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AR51" t="n">
         <v>395</v>
@@ -8641,13 +8629,13 @@
         <v>206.67</v>
       </c>
       <c r="T52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="U52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="V52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
@@ -8665,25 +8653,25 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AC52" t="n">
         <v>1</v>
       </c>
       <c r="AD52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AE52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AF52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="AG52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="AH52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -8701,16 +8689,16 @@
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO52" t="n">
         <v>1</v>
       </c>
       <c r="AP52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AQ52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AR52" t="n">
         <v>378</v>
@@ -8799,16 +8787,16 @@
         <v>313.64</v>
       </c>
       <c r="T53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="U53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -8829,19 +8817,19 @@
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AE53" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AF53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AG53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AH53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI53" t="n">
         <v>5</v>
@@ -8865,10 +8853,10 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ53" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AR53" t="n">
         <v>429</v>
@@ -8957,16 +8945,16 @@
         <v>3.57</v>
       </c>
       <c r="T54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="U54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X54" t="n">
         <v>22</v>
@@ -8990,19 +8978,19 @@
         <v>424</v>
       </c>
       <c r="AE54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AF54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AG54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AH54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ54" t="n">
         <v>22</v>
@@ -9026,7 +9014,7 @@
         <v>424</v>
       </c>
       <c r="AQ54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AR54" t="n">
         <v>396</v>
@@ -9115,25 +9103,25 @@
         <v>200</v>
       </c>
       <c r="T55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="V55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9148,28 +9136,28 @@
         <v>374</v>
       </c>
       <c r="AE55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AF55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AH55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM55" t="n">
         <v>0</v>
@@ -9184,7 +9172,7 @@
         <v>374</v>
       </c>
       <c r="AQ55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AR55" t="n">
         <v>279</v>
@@ -9273,19 +9261,19 @@
         <v>43.46</v>
       </c>
       <c r="T56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="U56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -9297,31 +9285,31 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AE56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AF56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AG56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="AH56" t="n">
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK56" t="n">
         <v>0</v>
@@ -9333,16 +9321,16 @@
         <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AO56" t="n">
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AQ56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AR56" t="n">
         <v>420</v>
@@ -9431,16 +9419,16 @@
         <v>100</v>
       </c>
       <c r="T57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="U57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="V57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X57" t="n">
         <v>1</v>
@@ -9455,28 +9443,28 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AE57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AF57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AH57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AI57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="n">
         <v>1</v>
@@ -9491,16 +9479,16 @@
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AQ57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AR57" t="n">
         <v>336</v>
@@ -9589,22 +9577,22 @@
         <v>265</v>
       </c>
       <c r="T58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="U58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="V58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -9613,34 +9601,34 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AC58" t="n">
         <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AE58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AF58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AG58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AH58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9649,16 +9637,16 @@
         <v>0</v>
       </c>
       <c r="AN58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AO58" t="n">
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AQ58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AR58" t="n">
         <v>363</v>
@@ -9747,16 +9735,16 @@
         <v>96.77</v>
       </c>
       <c r="T59" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="U59" t="n">
         <v>153</v>
       </c>
       <c r="V59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="W59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -9777,22 +9765,22 @@
         <v>4</v>
       </c>
       <c r="AD59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AE59" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AF59" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="AG59" t="n">
         <v>153</v>
       </c>
       <c r="AH59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AI59" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AJ59" t="n">
         <v>0</v>
@@ -9813,10 +9801,10 @@
         <v>4</v>
       </c>
       <c r="AP59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AQ59" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="AR59" t="n">
         <v>383</v>
@@ -9905,76 +9893,76 @@
         <v>22.22</v>
       </c>
       <c r="T60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="U60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AE60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AF60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AG60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH60" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AI60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
         <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AR60" t="n">
         <v>377</v>
@@ -10221,22 +10209,22 @@
         <v>293.33</v>
       </c>
       <c r="T62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="U62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="V62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
         <v>1</v>
       </c>
       <c r="X62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -10251,28 +10239,28 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AE62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AF62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AG62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="AH62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>1</v>
       </c>
       <c r="AJ62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10287,10 +10275,10 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AQ62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AR62" t="n">
         <v>365</v>
@@ -10379,13 +10367,13 @@
         <v>187.88</v>
       </c>
       <c r="T63" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="U63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="V63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W63" t="n">
         <v>0</v>
@@ -10409,19 +10397,19 @@
         <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AE63" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="AF63" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AG63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="AH63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -10445,10 +10433,10 @@
         <v>0</v>
       </c>
       <c r="AP63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AQ63" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AR63" t="n">
         <v>324</v>
@@ -10537,19 +10525,19 @@
         <v>142.86</v>
       </c>
       <c r="T64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="U64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" t="n">
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -10567,16 +10555,16 @@
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AE64" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AF64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AH64" t="n">
         <v>0</v>
@@ -10585,7 +10573,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK64" t="n">
         <v>0</v>
@@ -10603,10 +10591,10 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ64" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AR64" t="n">
         <v>440</v>
@@ -10695,19 +10683,19 @@
         <v>69.23</v>
       </c>
       <c r="T65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="V65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="W65" t="n">
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -10725,25 +10713,25 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AE65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AF65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AH65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK65" t="n">
         <v>0</v>
@@ -10761,10 +10749,10 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AR65" t="n">
         <v>417</v>
@@ -10853,19 +10841,19 @@
         <v>209.53</v>
       </c>
       <c r="T66" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="U66" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
@@ -10880,28 +10868,28 @@
         <v>21</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD66" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AE66" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="AF66" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AG66" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="AH66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK66" t="n">
         <v>0</v>
@@ -10919,10 +10907,10 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AQ66" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AR66" t="n">
         <v>384</v>
@@ -11011,19 +10999,19 @@
         <v>16.67</v>
       </c>
       <c r="T67" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="U67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="V67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="W67" t="n">
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
@@ -11041,25 +11029,25 @@
         <v>5</v>
       </c>
       <c r="AD67" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AE67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AF67" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="AG67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AH67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AK67" t="n">
         <v>0</v>
@@ -11077,10 +11065,10 @@
         <v>5</v>
       </c>
       <c r="AP67" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AQ67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AR67" t="n">
         <v>297</v>
@@ -11169,19 +11157,19 @@
         <v>45.29</v>
       </c>
       <c r="T68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="U68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="V68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="W68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
@@ -11193,31 +11181,31 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="AE68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AF68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="AG68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="AH68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AI68" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK68" t="n">
         <v>0</v>
@@ -11229,16 +11217,16 @@
         <v>0</v>
       </c>
       <c r="AN68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AQ68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AR68" t="n">
         <v>395</v>
@@ -11327,19 +11315,19 @@
         <v>162.5</v>
       </c>
       <c r="T69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="U69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="V69" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="W69" t="n">
         <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -11351,31 +11339,31 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AE69" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AF69" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AG69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AH69" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AI69" t="n">
         <v>1</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK69" t="n">
         <v>0</v>
@@ -11387,16 +11375,16 @@
         <v>0</v>
       </c>
       <c r="AN69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ69" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AR69" t="n">
         <v>317</v>
@@ -11485,19 +11473,19 @@
         <v>50</v>
       </c>
       <c r="T70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="U70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
@@ -11518,22 +11506,22 @@
         <v>346</v>
       </c>
       <c r="AE70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK70" t="n">
         <v>0</v>
@@ -11554,7 +11542,7 @@
         <v>346</v>
       </c>
       <c r="AQ70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AR70" t="n">
         <v>306</v>
@@ -11643,16 +11631,16 @@
         <v>144.29</v>
       </c>
       <c r="T71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="U71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -11673,22 +11661,22 @@
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AE71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AF71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="AG71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="AH71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AI71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AJ71" t="n">
         <v>0</v>
@@ -11709,10 +11697,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AQ71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AR71" t="n">
         <v>366</v>
@@ -11801,16 +11789,16 @@
         <v>428.74</v>
       </c>
       <c r="T72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="U72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="V72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -11831,22 +11819,22 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AE72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AF72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="AG72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="AH72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="n">
         <v>0</v>
@@ -11867,10 +11855,10 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AQ72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AR72" t="n">
         <v>353</v>
@@ -11959,10 +11947,10 @@
         <v>213.97</v>
       </c>
       <c r="T73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="U73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11983,22 +11971,22 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AC73" t="n">
         <v>1</v>
       </c>
       <c r="AD73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AE73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AF73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AG73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AH73" t="n">
         <v>0</v>
@@ -12019,16 +12007,16 @@
         <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AO73" t="n">
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AR73" t="n">
         <v>362</v>
@@ -12117,16 +12105,16 @@
         <v>310</v>
       </c>
       <c r="T74" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="V74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -12141,28 +12129,28 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC74" t="n">
         <v>1</v>
       </c>
       <c r="AD74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AE74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AF74" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AH74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AJ74" t="n">
         <v>0</v>
@@ -12177,16 +12165,16 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO74" t="n">
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AQ74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AR74" t="n">
         <v>398</v>
@@ -12275,55 +12263,55 @@
         <v>350</v>
       </c>
       <c r="T75" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="U75" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="V75" t="n">
+        <v>5</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>413</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>251</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>161</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>214</v>
+      </c>
+      <c r="AH75" t="n">
         <v>4</v>
       </c>
-      <c r="W75" t="n">
-        <v>3</v>
-      </c>
-      <c r="X75" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>411</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>245</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>164</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>202</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>3</v>
-      </c>
       <c r="AI75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AK75" t="n">
         <v>0</v>
@@ -12335,16 +12323,16 @@
         <v>0</v>
       </c>
       <c r="AN75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ75" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AR75" t="n">
         <v>359</v>
@@ -12433,13 +12421,13 @@
         <v>11.11</v>
       </c>
       <c r="T76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="U76" t="n">
         <v>133</v>
       </c>
       <c r="V76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="W76" t="n">
         <v>0</v>
@@ -12463,19 +12451,19 @@
         <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AE76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AF76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AG76" t="n">
         <v>133</v>
       </c>
       <c r="AH76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -12499,10 +12487,10 @@
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AQ76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AR76" t="n">
         <v>357</v>
@@ -12591,19 +12579,19 @@
         <v>218.57</v>
       </c>
       <c r="T77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="U77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="V77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77" t="n">
         <v>0</v>
@@ -12615,31 +12603,31 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AE77" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AF77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="AG77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="AH77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>9</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK77" t="n">
         <v>0</v>
@@ -12651,16 +12639,16 @@
         <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
       </c>
       <c r="AP77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AQ77" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="AR77" t="n">
         <v>386</v>
@@ -12749,19 +12737,19 @@
         <v>170</v>
       </c>
       <c r="T78" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="U78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="V78" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="W78" t="n">
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y78" t="n">
         <v>0</v>
@@ -12773,31 +12761,31 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC78" t="n">
         <v>1</v>
       </c>
       <c r="AD78" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AE78" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AF78" t="n">
         <v>150</v>
       </c>
       <c r="AG78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AH78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK78" t="n">
         <v>0</v>
@@ -12809,16 +12797,16 @@
         <v>0</v>
       </c>
       <c r="AN78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO78" t="n">
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AQ78" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AR78" t="n">
         <v>350</v>
@@ -12907,13 +12895,13 @@
         <v>127.97</v>
       </c>
       <c r="T79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
         <v>0</v>
@@ -12937,19 +12925,19 @@
         <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AE79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AF79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AG79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AH79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -12973,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AQ79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AR79" t="n">
         <v>319</v>
@@ -13068,7 +13056,7 @@
         <v>96</v>
       </c>
       <c r="U80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -13077,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -13104,7 +13092,7 @@
         <v>96</v>
       </c>
       <c r="AG80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH80" t="n">
         <v>0</v>
@@ -13113,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK80" t="n">
         <v>0</v>
@@ -13381,19 +13369,19 @@
         <v>112.5</v>
       </c>
       <c r="T82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="U82" t="n">
         <v>218</v>
       </c>
       <c r="V82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W82" t="n">
         <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
@@ -13411,25 +13399,25 @@
         <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AE82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AF82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AG82" t="n">
         <v>218</v>
       </c>
       <c r="AH82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK82" t="n">
         <v>0</v>
@@ -13447,10 +13435,10 @@
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AQ82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AR82" t="n">
         <v>385</v>
@@ -13539,19 +13527,19 @@
         <v>207.14</v>
       </c>
       <c r="T83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="U83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="V83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="W83" t="n">
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
@@ -13569,25 +13557,25 @@
         <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AE83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AF83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="AH83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AK83" t="n">
         <v>0</v>
@@ -13605,10 +13593,10 @@
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AR83" t="n">
         <v>340</v>
@@ -13697,16 +13685,16 @@
         <v>40</v>
       </c>
       <c r="T84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="U84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="V84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
@@ -13721,28 +13709,28 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AE84" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="AF84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AG84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="AH84" t="n">
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AJ84" t="n">
         <v>0</v>
@@ -13757,16 +13745,16 @@
         <v>0</v>
       </c>
       <c r="AN84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AO84" t="n">
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ84" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AR84" t="n">
         <v>378</v>
@@ -13855,13 +13843,13 @@
         <v>33.33</v>
       </c>
       <c r="T85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="U85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="V85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W85" t="n">
         <v>0</v>
@@ -13879,25 +13867,25 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AC85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AE85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AF85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AG85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AH85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -13915,16 +13903,16 @@
         <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AO85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AQ85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AR85" t="n">
         <v>367</v>
@@ -14013,22 +14001,22 @@
         <v>111.11</v>
       </c>
       <c r="T86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="V86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Y86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -14037,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14046,25 +14034,25 @@
         <v>447</v>
       </c>
       <c r="AE86" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AF86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AH86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AJ86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AK86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL86" t="n">
         <v>0</v>
@@ -14073,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="AN86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
@@ -14082,7 +14070,7 @@
         <v>447</v>
       </c>
       <c r="AQ86" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AR86" t="n">
         <v>367</v>
@@ -14171,16 +14159,16 @@
         <v>91.43000000000001</v>
       </c>
       <c r="T87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="U87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X87" t="n">
         <v>27</v>
@@ -14195,28 +14183,28 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AE87" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AF87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AG87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AH87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI87" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AJ87" t="n">
         <v>27</v>
@@ -14231,16 +14219,16 @@
         <v>0</v>
       </c>
       <c r="AN87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO87" t="n">
         <v>0</v>
       </c>
       <c r="AP87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ87" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AR87" t="n">
         <v>360</v>
@@ -14329,16 +14317,16 @@
         <v>233.33</v>
       </c>
       <c r="T88" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="U88" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="V88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="X88" t="n">
         <v>1</v>
@@ -14353,28 +14341,28 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="AE88" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="AF88" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AG88" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI88" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AJ88" t="n">
         <v>1</v>
@@ -14389,16 +14377,16 @@
         <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AQ88" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AR88" t="n">
         <v>356</v>
@@ -14487,19 +14475,19 @@
         <v>348.81</v>
       </c>
       <c r="T89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="U89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="V89" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="W89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -14511,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14520,22 +14508,22 @@
         <v>492</v>
       </c>
       <c r="AE89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AF89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AH89" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AI89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AJ89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK89" t="n">
         <v>0</v>
@@ -14547,7 +14535,7 @@
         <v>0</v>
       </c>
       <c r="AN89" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AO89" t="n">
         <v>0</v>
@@ -14556,7 +14544,7 @@
         <v>492</v>
       </c>
       <c r="AQ89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AR89" t="n">
         <v>405</v>
@@ -14645,16 +14633,16 @@
         <v>31.93</v>
       </c>
       <c r="T90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="U90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -14669,28 +14657,28 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>323</v>
       </c>
       <c r="AE90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AF90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AG90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AH90" t="n">
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AJ90" t="n">
         <v>0</v>
@@ -14705,16 +14693,16 @@
         <v>0</v>
       </c>
       <c r="AN90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP90" t="n">
         <v>323</v>
       </c>
       <c r="AQ90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AR90" t="n">
         <v>301</v>
@@ -14803,13 +14791,13 @@
         <v>90</v>
       </c>
       <c r="T91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="U91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="V91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W91" t="n">
         <v>0</v>
@@ -14833,19 +14821,19 @@
         <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AE91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AF91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AG91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="AH91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -14869,10 +14857,10 @@
         <v>0</v>
       </c>
       <c r="AP91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AQ91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AR91" t="n">
         <v>399</v>
@@ -14961,13 +14949,13 @@
         <v>259.65</v>
       </c>
       <c r="T92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="U92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="V92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
         <v>5</v>
@@ -14991,19 +14979,19 @@
         <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AE92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AF92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="AH92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>5</v>
@@ -15027,10 +15015,10 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AQ92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AR92" t="n">
         <v>364</v>
@@ -15119,10 +15107,10 @@
         <v>75</v>
       </c>
       <c r="T93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="U93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -15131,7 +15119,7 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -15149,16 +15137,16 @@
         <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AE93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AF93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AG93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AH93" t="n">
         <v>0</v>
@@ -15167,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
         <v>0</v>
@@ -15185,10 +15173,10 @@
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AQ93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AR93" t="n">
         <v>335</v>
@@ -15280,16 +15268,16 @@
         <v>198</v>
       </c>
       <c r="U94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="V94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -15301,7 +15289,7 @@
         <v>1</v>
       </c>
       <c r="AB94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15310,22 +15298,22 @@
         <v>408</v>
       </c>
       <c r="AE94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AF94" t="n">
         <v>198</v>
       </c>
       <c r="AG94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="AH94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK94" t="n">
         <v>0</v>
@@ -15337,7 +15325,7 @@
         <v>1</v>
       </c>
       <c r="AN94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AO94" t="n">
         <v>0</v>
@@ -15346,7 +15334,7 @@
         <v>408</v>
       </c>
       <c r="AQ94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AR94" t="n">
         <v>373</v>
@@ -15435,19 +15423,19 @@
         <v>500</v>
       </c>
       <c r="T95" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="U95" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="V95" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -15465,25 +15453,25 @@
         <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AE95" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AF95" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AG95" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AH95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK95" t="n">
         <v>0</v>
@@ -15501,10 +15489,10 @@
         <v>0</v>
       </c>
       <c r="AP95" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AQ95" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AR95" t="n">
         <v>356</v>
@@ -15593,19 +15581,19 @@
         <v>103.78</v>
       </c>
       <c r="T96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="U96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="V96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y96" t="n">
         <v>0</v>
@@ -15623,25 +15611,25 @@
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AE96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AF96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AG96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="AH96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK96" t="n">
         <v>0</v>
@@ -15659,10 +15647,10 @@
         <v>0</v>
       </c>
       <c r="AP96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AQ96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AR96" t="n">
         <v>282</v>
@@ -15751,49 +15739,49 @@
         <v>75</v>
       </c>
       <c r="T97" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="U97" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="V97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="W97" t="n">
         <v>44</v>
       </c>
       <c r="X97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AE97" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="AF97" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="AG97" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="AH97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AI97" t="n">
         <v>44</v>
@@ -15805,22 +15793,22 @@
         <v>0</v>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM97" t="n">
         <v>0</v>
       </c>
       <c r="AN97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AO97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AQ97" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AR97" t="n">
         <v>378</v>
@@ -15909,19 +15897,19 @@
         <v>36.84</v>
       </c>
       <c r="T98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="V98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W98" t="n">
         <v>9</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -15942,22 +15930,22 @@
         <v>399</v>
       </c>
       <c r="AE98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AF98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AH98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AI98" t="n">
         <v>9</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK98" t="n">
         <v>0</v>
@@ -15978,7 +15966,7 @@
         <v>399</v>
       </c>
       <c r="AQ98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AR98" t="n">
         <v>367</v>
@@ -16067,10 +16055,10 @@
         <v>183.33</v>
       </c>
       <c r="T99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="U99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -16079,7 +16067,7 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -16097,16 +16085,16 @@
         <v>2</v>
       </c>
       <c r="AD99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AE99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AF99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AG99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="AH99" t="n">
         <v>0</v>
@@ -16115,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
         <v>0</v>
@@ -16133,10 +16121,10 @@
         <v>2</v>
       </c>
       <c r="AP99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AQ99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AR99" t="n">
         <v>321</v>
@@ -16225,19 +16213,19 @@
         <v>50</v>
       </c>
       <c r="T100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="U100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="V100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W100" t="n">
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
         <v>0</v>
@@ -16249,31 +16237,31 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AE100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AF100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AG100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AH100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK100" t="n">
         <v>0</v>
@@ -16285,16 +16273,16 @@
         <v>0</v>
       </c>
       <c r="AN100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AQ100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AR100" t="n">
         <v>343</v>
@@ -16383,58 +16371,58 @@
         <v>78.2</v>
       </c>
       <c r="T101" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="U101" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W101" t="n">
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>84</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>509</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>311</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>199</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>219</v>
+      </c>
+      <c r="AH101" t="n">
         <v>2</v>
       </c>
-      <c r="Z101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>502</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>212</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>203</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>0</v>
-      </c>
       <c r="AI101" t="n">
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL101" t="n">
         <v>1</v>
@@ -16443,16 +16431,16 @@
         <v>0</v>
       </c>
       <c r="AN101" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AO101" t="n">
         <v>1</v>
       </c>
       <c r="AP101" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AQ101" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AR101" t="n">
         <v>455</v>
@@ -16541,13 +16529,13 @@
         <v>316.67</v>
       </c>
       <c r="T102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="U102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="V102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="W102" t="n">
         <v>5</v>
@@ -16571,19 +16559,19 @@
         <v>2</v>
       </c>
       <c r="AD102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AE102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AF102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AH102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI102" t="n">
         <v>5</v>
@@ -16607,10 +16595,10 @@
         <v>2</v>
       </c>
       <c r="AP102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AR102" t="n">
         <v>472</v>
@@ -16699,10 +16687,10 @@
         <v>26.5</v>
       </c>
       <c r="T103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="U103" t="n">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -16711,7 +16699,7 @@
         <v>1</v>
       </c>
       <c r="X103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
@@ -16729,25 +16717,25 @@
         <v>1</v>
       </c>
       <c r="AD103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AE103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AF103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AG103" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI103" t="n">
         <v>1</v>
       </c>
       <c r="AJ103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
         <v>0</v>
@@ -16765,10 +16753,10 @@
         <v>1</v>
       </c>
       <c r="AP103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AQ103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AR103" t="n">
         <v>316</v>
@@ -16857,19 +16845,19 @@
         <v>33.33</v>
       </c>
       <c r="T104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="W104" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="X104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y104" t="n">
         <v>0</v>
@@ -16887,25 +16875,25 @@
         <v>3</v>
       </c>
       <c r="AD104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AE104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AF104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AH104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AI104" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AJ104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK104" t="n">
         <v>0</v>
@@ -16923,10 +16911,10 @@
         <v>3</v>
       </c>
       <c r="AP104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AQ104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AR104" t="n">
         <v>422</v>
@@ -17015,16 +17003,16 @@
         <v>150</v>
       </c>
       <c r="T105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="U105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="V105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="W105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -17045,22 +17033,22 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AE105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AF105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AG105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AH105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AI105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AJ105" t="n">
         <v>0</v>
@@ -17081,10 +17069,10 @@
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AQ105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AR105" t="n">
         <v>391</v>
@@ -17173,10 +17161,10 @@
         <v>483.33</v>
       </c>
       <c r="T106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="U106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -17185,7 +17173,7 @@
         <v>1</v>
       </c>
       <c r="X106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -17197,22 +17185,22 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AE106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AF106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AH106" t="n">
         <v>0</v>
@@ -17221,7 +17209,7 @@
         <v>1</v>
       </c>
       <c r="AJ106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK106" t="n">
         <v>0</v>
@@ -17233,16 +17221,16 @@
         <v>0</v>
       </c>
       <c r="AN106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO106" t="n">
         <v>0</v>
       </c>
       <c r="AP106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AQ106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AR106" t="n">
         <v>366</v>
@@ -17331,13 +17319,13 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="U107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="V107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W107" t="n">
         <v>0</v>
@@ -17364,16 +17352,16 @@
         <v>367</v>
       </c>
       <c r="AE107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AF107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AG107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="AH107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -17400,7 +17388,7 @@
         <v>367</v>
       </c>
       <c r="AQ107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AR107" t="n">
         <v>322</v>
@@ -17489,19 +17477,19 @@
         <v>378.78</v>
       </c>
       <c r="T108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="U108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="V108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W108" t="n">
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -17522,22 +17510,22 @@
         <v>382</v>
       </c>
       <c r="AE108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AF108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AG108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="AH108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK108" t="n">
         <v>0</v>
@@ -17558,7 +17546,7 @@
         <v>382</v>
       </c>
       <c r="AQ108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AR108" t="n">
         <v>324</v>
@@ -17647,19 +17635,19 @@
         <v>65.3</v>
       </c>
       <c r="T109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="U109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="V109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="W109" t="n">
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -17671,31 +17659,31 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AC109" t="n">
         <v>1</v>
       </c>
       <c r="AD109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AE109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AF109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AG109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AH109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK109" t="n">
         <v>0</v>
@@ -17707,16 +17695,16 @@
         <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AO109" t="n">
         <v>1</v>
       </c>
       <c r="AP109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AQ109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AR109" t="n">
         <v>407</v>
@@ -17805,19 +17793,19 @@
         <v>491.15</v>
       </c>
       <c r="T110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="U110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="V110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
         <v>5</v>
       </c>
       <c r="X110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -17832,28 +17820,28 @@
         <v>20</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD110" t="n">
         <v>622</v>
       </c>
       <c r="AE110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AF110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AH110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>5</v>
       </c>
       <c r="AJ110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK110" t="n">
         <v>0</v>
@@ -17868,13 +17856,13 @@
         <v>20</v>
       </c>
       <c r="AO110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP110" t="n">
         <v>622</v>
       </c>
       <c r="AQ110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AR110" t="n">
         <v>507</v>
@@ -17963,13 +17951,13 @@
         <v>4.35</v>
       </c>
       <c r="T111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="U111" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="V111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W111" t="n">
         <v>2</v>
@@ -17993,19 +17981,19 @@
         <v>0</v>
       </c>
       <c r="AD111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AE111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AF111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG111" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI111" t="n">
         <v>2</v>
@@ -18029,10 +18017,10 @@
         <v>0</v>
       </c>
       <c r="AP111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AQ111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AR111" t="n">
         <v>294</v>
@@ -18121,10 +18109,10 @@
         <v>166.67</v>
       </c>
       <c r="T112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="U112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -18145,22 +18133,22 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AE112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AF112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AG112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AH112" t="n">
         <v>0</v>
@@ -18181,16 +18169,16 @@
         <v>0</v>
       </c>
       <c r="AN112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO112" t="n">
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AQ112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AR112" t="n">
         <v>403</v>
@@ -18279,19 +18267,19 @@
         <v>238.18</v>
       </c>
       <c r="T113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="U113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="V113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="W113" t="n">
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
@@ -18303,31 +18291,31 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AE113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AF113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="AG113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="AH113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AK113" t="n">
         <v>0</v>
@@ -18339,16 +18327,16 @@
         <v>0</v>
       </c>
       <c r="AN113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AO113" t="n">
         <v>0</v>
       </c>
       <c r="AP113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AQ113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AR113" t="n">
         <v>362</v>
@@ -18440,10 +18428,10 @@
         <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="V114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="W114" t="n">
         <v>0</v>
@@ -18461,7 +18449,7 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AC114" t="n">
         <v>4</v>
@@ -18476,10 +18464,10 @@
         <v>0</v>
       </c>
       <c r="AG114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="AH114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -18497,7 +18485,7 @@
         <v>0</v>
       </c>
       <c r="AN114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO114" t="n">
         <v>4</v>
@@ -18598,7 +18586,7 @@
         <v>212</v>
       </c>
       <c r="U115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="V115" t="n">
         <v>6</v>
@@ -18619,7 +18607,7 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -18634,7 +18622,7 @@
         <v>212</v>
       </c>
       <c r="AG115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AH115" t="n">
         <v>6</v>
@@ -18655,7 +18643,7 @@
         <v>0</v>
       </c>
       <c r="AN115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO115" t="n">
         <v>0</v>
@@ -18753,13 +18741,13 @@
         <v>44</v>
       </c>
       <c r="T116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="U116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="V116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
         <v>0</v>
@@ -18783,19 +18771,19 @@
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AE116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AF116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AG116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AH116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
@@ -18819,10 +18807,10 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AQ116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AR116" t="n">
         <v>333</v>
@@ -18911,19 +18899,19 @@
         <v>383.34</v>
       </c>
       <c r="T117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="U117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="V117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
@@ -18935,31 +18923,31 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AE117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AF117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AG117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AH117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK117" t="n">
         <v>0</v>
@@ -18971,16 +18959,16 @@
         <v>0</v>
       </c>
       <c r="AN117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AO117" t="n">
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AR117" t="n">
         <v>364</v>
@@ -19069,16 +19057,16 @@
         <v>250</v>
       </c>
       <c r="T118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="U118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="V118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -19099,22 +19087,22 @@
         <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AE118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AF118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AG118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="AH118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ118" t="n">
         <v>0</v>
@@ -19135,10 +19123,10 @@
         <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AQ118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AR118" t="n">
         <v>378</v>
@@ -19227,13 +19215,13 @@
         <v>23.33</v>
       </c>
       <c r="T119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="U119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="V119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -19257,19 +19245,19 @@
         <v>3</v>
       </c>
       <c r="AD119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AE119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AF119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AG119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="AH119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -19293,10 +19281,10 @@
         <v>3</v>
       </c>
       <c r="AP119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AQ119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AR119" t="n">
         <v>420</v>
@@ -19385,76 +19373,76 @@
         <v>183.33</v>
       </c>
       <c r="T120" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="U120" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W120" t="n">
+        <v>2</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
         <v>3</v>
       </c>
-      <c r="X120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y120" t="n">
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>511</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>273</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>236</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>181</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI120" t="n">
         <v>2</v>
       </c>
-      <c r="Z120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>56</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>509</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>254</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>169</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI120" t="n">
+      <c r="AJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL120" t="n">
         <v>3</v>
       </c>
-      <c r="AJ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>2</v>
-      </c>
       <c r="AM120" t="n">
         <v>0</v>
       </c>
       <c r="AN120" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO120" t="n">
         <v>0</v>
       </c>
       <c r="AP120" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AQ120" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AR120" t="n">
         <v>430</v>
@@ -19543,19 +19531,19 @@
         <v>140.76</v>
       </c>
       <c r="T121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="U121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="V121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
         <v>0</v>
@@ -19567,31 +19555,31 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AE121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AF121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AH121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK121" t="n">
         <v>0</v>
@@ -19603,16 +19591,16 @@
         <v>0</v>
       </c>
       <c r="AN121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AO121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AR121" t="n">
         <v>379</v>
@@ -19701,10 +19689,10 @@
         <v>59.53</v>
       </c>
       <c r="T122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="U122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="V122" t="n">
         <v>2</v>
@@ -19713,7 +19701,7 @@
         <v>1</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y122" t="n">
         <v>0</v>
@@ -19731,16 +19719,16 @@
         <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AE122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AF122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="AG122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AH122" t="n">
         <v>2</v>
@@ -19749,7 +19737,7 @@
         <v>1</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK122" t="n">
         <v>0</v>
@@ -19767,10 +19755,10 @@
         <v>0</v>
       </c>
       <c r="AP122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AR122" t="n">
         <v>419</v>
@@ -19859,13 +19847,13 @@
         <v>118.56</v>
       </c>
       <c r="T123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="U123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="V123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W123" t="n">
         <v>5</v>
@@ -19874,7 +19862,7 @@
         <v>1</v>
       </c>
       <c r="Y123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -19892,16 +19880,16 @@
         <v>493</v>
       </c>
       <c r="AE123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AF123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AG123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AH123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI123" t="n">
         <v>5</v>
@@ -19910,7 +19898,7 @@
         <v>1</v>
       </c>
       <c r="AK123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL123" t="n">
         <v>0</v>
@@ -19928,7 +19916,7 @@
         <v>493</v>
       </c>
       <c r="AQ123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AR123" t="n">
         <v>432</v>
@@ -20017,13 +20005,13 @@
         <v>291.07</v>
       </c>
       <c r="T124" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="V124" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
         <v>4</v>
@@ -20047,19 +20035,19 @@
         <v>1</v>
       </c>
       <c r="AD124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AE124" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AF124" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AG124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AH124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>4</v>
@@ -20083,10 +20071,10 @@
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ124" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AR124" t="n">
         <v>437</v>
@@ -20175,19 +20163,19 @@
         <v>166.67</v>
       </c>
       <c r="T125" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="U125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="V125" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -20205,25 +20193,25 @@
         <v>2</v>
       </c>
       <c r="AD125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AE125" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="AF125" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="AG125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="AH125" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK125" t="n">
         <v>0</v>
@@ -20241,10 +20229,10 @@
         <v>2</v>
       </c>
       <c r="AP125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AQ125" t="n">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="AR125" t="n">
         <v>303</v>
@@ -20333,10 +20321,10 @@
         <v>140</v>
       </c>
       <c r="T126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="U126" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -20357,25 +20345,25 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AE126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AF126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AG126" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AH126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI126" t="n">
         <v>0</v>
@@ -20393,16 +20381,16 @@
         <v>0</v>
       </c>
       <c r="AN126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AO126" t="n">
         <v>0</v>
       </c>
       <c r="AP126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AQ126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AR126" t="n">
         <v>366</v>
@@ -20491,16 +20479,16 @@
         <v>875</v>
       </c>
       <c r="T127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="U127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X127" t="n">
         <v>2</v>
@@ -20521,22 +20509,22 @@
         <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AE127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AF127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AG127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AH127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AJ127" t="n">
         <v>2</v>
@@ -20557,10 +20545,10 @@
         <v>0</v>
       </c>
       <c r="AP127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AR127" t="n">
         <v>394</v>
@@ -20652,13 +20640,13 @@
         <v>180</v>
       </c>
       <c r="U128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="V128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="W128" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="X128" t="n">
         <v>2</v>
@@ -20673,7 +20661,7 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -20682,19 +20670,19 @@
         <v>470</v>
       </c>
       <c r="AE128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AF128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AH128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AI128" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ128" t="n">
         <v>2</v>
@@ -20709,7 +20697,7 @@
         <v>0</v>
       </c>
       <c r="AN128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AO128" t="n">
         <v>0</v>
@@ -20718,7 +20706,7 @@
         <v>470</v>
       </c>
       <c r="AQ128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AR128" t="n">
         <v>372</v>
@@ -20807,13 +20795,13 @@
         <v>69.69</v>
       </c>
       <c r="T129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="U129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W129" t="n">
         <v>0</v>
@@ -20840,16 +20828,16 @@
         <v>345</v>
       </c>
       <c r="AE129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AF129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="AG129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -20876,7 +20864,7 @@
         <v>345</v>
       </c>
       <c r="AQ129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AR129" t="n">
         <v>313</v>
@@ -20965,19 +20953,19 @@
         <v>66.67</v>
       </c>
       <c r="T130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="U130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="V130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -20995,25 +20983,25 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AE130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AF130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="AG130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="AH130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AI130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AJ130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK130" t="n">
         <v>0</v>
@@ -21031,10 +21019,10 @@
         <v>0</v>
       </c>
       <c r="AP130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AR130" t="n">
         <v>386</v>
@@ -21123,13 +21111,13 @@
         <v>120</v>
       </c>
       <c r="T131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="U131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="V131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
         <v>1</v>
@@ -21147,7 +21135,7 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -21156,16 +21144,16 @@
         <v>399</v>
       </c>
       <c r="AE131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AF131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AH131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI131" t="n">
         <v>1</v>
@@ -21183,7 +21171,7 @@
         <v>0</v>
       </c>
       <c r="AN131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AO131" t="n">
         <v>0</v>
@@ -21192,7 +21180,7 @@
         <v>399</v>
       </c>
       <c r="AQ131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AR131" t="n">
         <v>370</v>
@@ -21281,13 +21269,13 @@
         <v>208.33</v>
       </c>
       <c r="T132" t="n">
+        <v>182</v>
+      </c>
+      <c r="U132" t="n">
         <v>188</v>
       </c>
-      <c r="U132" t="n">
-        <v>189</v>
-      </c>
       <c r="V132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -21305,25 +21293,25 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC132" t="n">
         <v>1</v>
       </c>
       <c r="AD132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AE132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AF132" t="n">
+        <v>182</v>
+      </c>
+      <c r="AG132" t="n">
         <v>188</v>
       </c>
-      <c r="AG132" t="n">
-        <v>189</v>
-      </c>
       <c r="AH132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -21341,16 +21329,16 @@
         <v>0</v>
       </c>
       <c r="AN132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AO132" t="n">
         <v>1</v>
       </c>
       <c r="AP132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AR132" t="n">
         <v>368</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,242 +429,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_USAHA PERUSAHAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,246 +413,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV132"/>
+  <dimension ref="A1:AV133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -813,19 +801,19 @@
         <v>447</v>
       </c>
       <c r="AR2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1129,7 +1117,7 @@
         <v>342</v>
       </c>
       <c r="AR4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -1141,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1287,7 +1275,7 @@
         <v>249</v>
       </c>
       <c r="AR5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -1296,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1445,7 +1433,7 @@
         <v>233</v>
       </c>
       <c r="AR6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -1457,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1603,19 +1591,19 @@
         <v>395</v>
       </c>
       <c r="AR7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1761,19 +1749,19 @@
         <v>285</v>
       </c>
       <c r="AR8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1919,19 +1907,19 @@
         <v>389</v>
       </c>
       <c r="AR9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -2077,19 +2065,19 @@
         <v>278</v>
       </c>
       <c r="AR10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2235,19 +2223,19 @@
         <v>271</v>
       </c>
       <c r="AR11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2393,19 +2381,19 @@
         <v>386</v>
       </c>
       <c r="AR12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2551,19 +2539,19 @@
         <v>493</v>
       </c>
       <c r="AR13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2709,19 +2697,19 @@
         <v>347</v>
       </c>
       <c r="AR14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2867,19 +2855,19 @@
         <v>308</v>
       </c>
       <c r="AR15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -3025,19 +3013,19 @@
         <v>382</v>
       </c>
       <c r="AR16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -3114,7 +3102,7 @@
         <v>71</v>
       </c>
       <c r="U17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="V17" t="n">
         <v>2</v>
@@ -3135,22 +3123,22 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AE17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AF17" t="n">
         <v>71</v>
       </c>
       <c r="AG17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -3171,31 +3159,31 @@
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AQ17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AR17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -3341,19 +3329,19 @@
         <v>377</v>
       </c>
       <c r="AR18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3499,19 +3487,19 @@
         <v>318</v>
       </c>
       <c r="AR19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3657,19 +3645,19 @@
         <v>307</v>
       </c>
       <c r="AR20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3815,19 +3803,19 @@
         <v>253</v>
       </c>
       <c r="AR21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3862,19 +3850,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>46.89</v>
+        <v>16.89</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>35.98999999999999</v>
+        <v>28.85</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -3883,37 +3871,37 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O22" t="n">
-        <v>219.24</v>
+        <v>224.95</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.68</v>
+        <v>37.68</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>104.57</v>
+        <v>54.57</v>
       </c>
       <c r="T22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="U22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3925,31 +3913,31 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AE22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AF22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="AG22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="AH22" t="n">
         <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3961,31 +3949,31 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AQ22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AR22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -4131,19 +4119,19 @@
         <v>423</v>
       </c>
       <c r="AR23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -4289,19 +4277,19 @@
         <v>282</v>
       </c>
       <c r="AR24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -4447,25 +4435,25 @@
         <v>368</v>
       </c>
       <c r="AR25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4494,13 +4482,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -4509,43 +4497,43 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>40</v>
-      </c>
-      <c r="N26" t="n">
-        <v>11</v>
-      </c>
       <c r="O26" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="R26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="T26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -4557,31 +4545,31 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AE26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="AF26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4593,31 +4581,31 @@
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AQ26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AR26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4763,19 +4751,19 @@
         <v>387</v>
       </c>
       <c r="AR27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AS27" t="n">
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -4921,10 +4909,10 @@
         <v>375</v>
       </c>
       <c r="AR28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -4933,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -5079,19 +5067,19 @@
         <v>343</v>
       </c>
       <c r="AR29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -5237,19 +5225,19 @@
         <v>380</v>
       </c>
       <c r="AR30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -5395,19 +5383,19 @@
         <v>201</v>
       </c>
       <c r="AR31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -5553,19 +5541,19 @@
         <v>281</v>
       </c>
       <c r="AR32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -5711,19 +5699,19 @@
         <v>282</v>
       </c>
       <c r="AR33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AS33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -5869,19 +5857,19 @@
         <v>450</v>
       </c>
       <c r="AR34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AS34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AT34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -6027,19 +6015,19 @@
         <v>243</v>
       </c>
       <c r="AR35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -6185,19 +6173,19 @@
         <v>477</v>
       </c>
       <c r="AR36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AS36" t="n">
         <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -6343,19 +6331,19 @@
         <v>518</v>
       </c>
       <c r="AR37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -6386,7 +6374,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6501,19 +6489,19 @@
         <v>365</v>
       </c>
       <c r="AR38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AS38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AT38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -6544,7 +6532,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6659,19 +6647,19 @@
         <v>313</v>
       </c>
       <c r="AR39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT39" t="n">
         <v>4</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -6817,19 +6805,19 @@
         <v>399</v>
       </c>
       <c r="AR40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -6975,19 +6963,19 @@
         <v>350</v>
       </c>
       <c r="AR41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AS41" t="n">
         <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -7133,19 +7121,19 @@
         <v>387</v>
       </c>
       <c r="AR42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -7291,7 +7279,7 @@
         <v>388</v>
       </c>
       <c r="AR43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -7300,10 +7288,10 @@
         <v>13</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -7449,7 +7437,7 @@
         <v>381</v>
       </c>
       <c r="AR44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
@@ -7458,57 +7446,57 @@
         <v>9</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>3.23</v>
+        <v>195.24</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -7517,195 +7505,195 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>328.57</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="R45" t="n">
+        <v>8</v>
+      </c>
+      <c r="S45" t="n">
+        <v>209.53</v>
+      </c>
+      <c r="T45" t="n">
+        <v>146</v>
+      </c>
+      <c r="U45" t="n">
+        <v>236</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>15</v>
+      </c>
+      <c r="X45" t="n">
         <v>3</v>
       </c>
-      <c r="O45" t="n">
-        <v>103.23</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="T45" t="n">
-        <v>85</v>
-      </c>
-      <c r="U45" t="n">
-        <v>329</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>7</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
       <c r="Y45" t="n">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AE45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AF45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AG45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="AH45" t="n">
         <v>1</v>
       </c>
       <c r="AI45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="n">
         <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AQ45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AR45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H46" t="n">
+        <v>19</v>
+      </c>
+      <c r="I46" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>23</v>
+      </c>
+      <c r="O46" t="n">
+        <v>267.31</v>
+      </c>
+      <c r="P46" t="n">
         <v>7</v>
       </c>
-      <c r="I46" t="n">
-        <v>195.24</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3</v>
-      </c>
-      <c r="K46" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>328.57</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
       <c r="Q46" t="n">
-        <v>14.29</v>
+        <v>78.8</v>
       </c>
       <c r="R46" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="S46" t="n">
-        <v>209.53</v>
+        <v>270.72</v>
       </c>
       <c r="T46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="U46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -7717,31 +7705,31 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AC46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="AE46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AF46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AG46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AH46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
@@ -7753,311 +7741,311 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AO46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AQ46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AR46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AS46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AT46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H47" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>191.9</v>
+        <v>65</v>
       </c>
       <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>150</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>70</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
         <v>4</v>
       </c>
-      <c r="K47" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>23</v>
-      </c>
-      <c r="O47" t="n">
-        <v>267.31</v>
-      </c>
-      <c r="P47" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>26</v>
-      </c>
       <c r="S47" t="n">
-        <v>270.72</v>
+        <v>65</v>
       </c>
       <c r="T47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="U47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AE47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AF47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AG47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AI47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AQ47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AR47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AS47" t="n">
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
+        <v>209</v>
+      </c>
+      <c r="H48" t="n">
+        <v>54</v>
+      </c>
+      <c r="I48" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="L48" t="n">
+        <v>32</v>
+      </c>
+      <c r="M48" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="N48" t="n">
         <v>27</v>
       </c>
-      <c r="H48" t="n">
+      <c r="O48" t="n">
+        <v>108.09</v>
+      </c>
+      <c r="P48" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="R48" t="n">
+        <v>93</v>
+      </c>
+      <c r="S48" t="n">
+        <v>142.58</v>
+      </c>
+      <c r="T48" t="n">
+        <v>121</v>
+      </c>
+      <c r="U48" t="n">
+        <v>334</v>
+      </c>
+      <c r="V48" t="n">
         <v>4</v>
       </c>
-      <c r="I48" t="n">
-        <v>65</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>150</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>5</v>
-      </c>
-      <c r="N48" t="n">
-        <v>5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>70</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>485</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>364</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>121</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>334</v>
+      </c>
+      <c r="AH48" t="n">
         <v>4</v>
       </c>
-      <c r="S48" t="n">
-        <v>65</v>
-      </c>
-      <c r="T48" t="n">
-        <v>128</v>
-      </c>
-      <c r="U48" t="n">
-        <v>218</v>
-      </c>
-      <c r="V48" t="n">
-        <v>35</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>428</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>299</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>128</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>218</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>35</v>
-      </c>
       <c r="AI48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -8069,19 +8057,19 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AQ48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AR48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -8090,209 +8078,209 @@
         <v>4</v>
       </c>
       <c r="AU48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="H49" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>81.97</v>
+        <v>108.33</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7</v>
+      </c>
+      <c r="O49" t="n">
+        <v>225</v>
+      </c>
+      <c r="P49" t="n">
         <v>10</v>
       </c>
-      <c r="K49" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="L49" t="n">
-        <v>32</v>
-      </c>
-      <c r="M49" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N49" t="n">
-        <v>27</v>
-      </c>
-      <c r="O49" t="n">
-        <v>108.09</v>
-      </c>
-      <c r="P49" t="n">
-        <v>39</v>
-      </c>
       <c r="Q49" t="n">
-        <v>60.62</v>
+        <v>225</v>
       </c>
       <c r="R49" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="S49" t="n">
-        <v>142.58</v>
+        <v>333.33</v>
       </c>
       <c r="T49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="U49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="V49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AE49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AF49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="AG49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="AH49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AO49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AQ49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AR49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>108.33</v>
+        <v>75</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -8301,356 +8289,356 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>225</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q50" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="R50" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S50" t="n">
-        <v>333.33</v>
+        <v>375</v>
       </c>
       <c r="T50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="U50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="V50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AE50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AF50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="AG50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="AH50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AO50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AQ50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AR50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>32</v>
+      </c>
+      <c r="H51" t="n">
+        <v>9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>150.68</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>40</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" t="n">
+        <v>106.67</v>
+      </c>
+      <c r="P51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>186.67</v>
+      </c>
+      <c r="R51" t="n">
+        <v>14</v>
+      </c>
+      <c r="S51" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="T51" t="n">
+        <v>89</v>
+      </c>
+      <c r="U51" t="n">
+        <v>331</v>
+      </c>
+      <c r="V51" t="n">
         <v>8</v>
       </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>75</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
+      <c r="W51" t="n">
         <v>3</v>
       </c>
-      <c r="O51" t="n">
-        <v>225</v>
-      </c>
-      <c r="P51" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>300</v>
-      </c>
-      <c r="R51" t="n">
-        <v>11</v>
-      </c>
-      <c r="S51" t="n">
-        <v>375</v>
-      </c>
-      <c r="T51" t="n">
-        <v>61</v>
-      </c>
-      <c r="U51" t="n">
-        <v>398</v>
-      </c>
-      <c r="V51" t="n">
-        <v>7</v>
-      </c>
-      <c r="W51" t="n">
-        <v>18</v>
-      </c>
       <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>331</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI51" t="n">
         <v>3</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>61</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>398</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AS51" t="n">
         <v>3</v>
       </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
       <c r="AT51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AU51" t="n">
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
+        <v>12</v>
+      </c>
+      <c r="I52" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7.579999999999999</v>
+      </c>
+      <c r="N52" t="n">
         <v>9</v>
       </c>
-      <c r="I52" t="n">
-        <v>150.68</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" t="n">
-        <v>40</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>6</v>
-      </c>
       <c r="O52" t="n">
-        <v>106.67</v>
+        <v>136.36</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q52" t="n">
-        <v>186.67</v>
+        <v>200</v>
       </c>
       <c r="R52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S52" t="n">
-        <v>337.35</v>
+        <v>245.45</v>
       </c>
       <c r="T52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="U52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="V52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -8659,34 +8647,34 @@
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AC52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AE52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AF52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="AH52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
@@ -8695,28 +8683,28 @@
         <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM52" t="n">
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AO52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AQ52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AR52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT52" t="n">
         <v>0</v>
@@ -8725,28 +8713,28 @@
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8760,171 +8748,171 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>78.78</v>
+        <v>266.67</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.579999999999999</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O53" t="n">
-        <v>203.03</v>
+        <v>266.67</v>
       </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q53" t="n">
-        <v>266.67</v>
+        <v>233.33</v>
       </c>
       <c r="R53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S53" t="n">
-        <v>345.45</v>
+        <v>500</v>
       </c>
       <c r="T53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AE53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AF53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AG53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK53" t="n">
         <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
         <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AQ53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AR53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AS53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AT53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AU53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AV53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>270.24</v>
+        <v>150</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -8942,37 +8930,37 @@
         <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>166.67</v>
+        <v>200</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="n">
-        <v>133.33</v>
+        <v>250</v>
       </c>
       <c r="R54" t="n">
         <v>9</v>
       </c>
       <c r="S54" t="n">
-        <v>403.57</v>
+        <v>400</v>
       </c>
       <c r="T54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="U54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8981,34 +8969,34 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AE54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AF54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AG54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9017,72 +9005,72 @@
         <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AQ54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AR54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AS54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I55" t="n">
-        <v>150</v>
+        <v>29.38</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9091,46 +9079,46 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O55" t="n">
-        <v>200</v>
+        <v>172.28</v>
       </c>
       <c r="P55" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="Q55" t="n">
-        <v>250</v>
+        <v>343.88</v>
       </c>
       <c r="R55" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="S55" t="n">
-        <v>400</v>
+        <v>373.26</v>
       </c>
       <c r="T55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="U55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -9139,34 +9127,34 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AE55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AF55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AG55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AJ55" t="n">
         <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9175,117 +9163,117 @@
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AO55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AQ55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AR55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AU55" t="n">
         <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="H56" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>29.38</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>32.14</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>172.28</v>
+        <v>242.86</v>
       </c>
       <c r="P56" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>343.88</v>
+        <v>296.43</v>
       </c>
       <c r="R56" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="S56" t="n">
-        <v>373.26</v>
+        <v>375</v>
       </c>
       <c r="T56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="U56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="W56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -9297,31 +9285,31 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
       <c r="AD56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AE56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AF56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AG56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="AH56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AI56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK56" t="n">
         <v>0</v>
@@ -9333,117 +9321,117 @@
         <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AO56" t="n">
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AQ56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AR56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>78.56999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>103.23</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R57" t="n">
         <v>2</v>
       </c>
-      <c r="K57" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>8</v>
-      </c>
-      <c r="O57" t="n">
-        <v>242.86</v>
-      </c>
-      <c r="P57" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>296.43</v>
-      </c>
-      <c r="R57" t="n">
-        <v>14</v>
-      </c>
       <c r="S57" t="n">
-        <v>375</v>
+        <v>6.45</v>
       </c>
       <c r="T57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="U57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="V57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="X57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -9455,31 +9443,31 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AC57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AE57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AF57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="AG57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="AH57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AI57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
         <v>0</v>
@@ -9491,31 +9479,31 @@
         <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AO57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AQ57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AR57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AS57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="n">
         <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -9661,19 +9649,19 @@
         <v>267</v>
       </c>
       <c r="AR58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AS58" t="n">
         <v>0</v>
       </c>
       <c r="AT58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -9819,19 +9807,19 @@
         <v>364</v>
       </c>
       <c r="AR59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AS59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="n">
         <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -9977,19 +9965,19 @@
         <v>289</v>
       </c>
       <c r="AR60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -10135,19 +10123,19 @@
         <v>238</v>
       </c>
       <c r="AR61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AS61" t="n">
         <v>0</v>
       </c>
       <c r="AT61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -10293,19 +10281,19 @@
         <v>440</v>
       </c>
       <c r="AR62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AU62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AV62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -10451,19 +10439,19 @@
         <v>373</v>
       </c>
       <c r="AR63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AS63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -10609,19 +10597,19 @@
         <v>394</v>
       </c>
       <c r="AR64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AS64" t="n">
         <v>0</v>
       </c>
       <c r="AT64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -10767,19 +10755,19 @@
         <v>357</v>
       </c>
       <c r="AR65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AS65" t="n">
         <v>0</v>
       </c>
       <c r="AT65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -10925,19 +10913,19 @@
         <v>397</v>
       </c>
       <c r="AR66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AS66" t="n">
         <v>0</v>
       </c>
       <c r="AT66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -11083,19 +11071,19 @@
         <v>255</v>
       </c>
       <c r="AR67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AS67" t="n">
         <v>0</v>
       </c>
       <c r="AT67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AU67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AV67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -11241,19 +11229,19 @@
         <v>504</v>
       </c>
       <c r="AR68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AU68" t="n">
         <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -11399,19 +11387,19 @@
         <v>300</v>
       </c>
       <c r="AR69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AS69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AU69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -11557,19 +11545,19 @@
         <v>224</v>
       </c>
       <c r="AR70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AS70" t="n">
         <v>0</v>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="n">
         <v>0</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -11715,19 +11703,19 @@
         <v>441</v>
       </c>
       <c r="AR71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AS71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU71" t="n">
         <v>0</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -11873,19 +11861,19 @@
         <v>578</v>
       </c>
       <c r="AR72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AS72" t="n">
         <v>0</v>
       </c>
       <c r="AT72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -12031,19 +12019,19 @@
         <v>331</v>
       </c>
       <c r="AR73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AS73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="n">
         <v>0</v>
       </c>
       <c r="AV73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -12189,10 +12177,10 @@
         <v>472</v>
       </c>
       <c r="AR74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AS74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AT74" t="n">
         <v>0</v>
@@ -12201,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -12347,19 +12335,19 @@
         <v>283</v>
       </c>
       <c r="AR75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AS75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AT75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -12505,19 +12493,19 @@
         <v>251</v>
       </c>
       <c r="AR76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AS76" t="n">
         <v>0</v>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -12663,19 +12651,19 @@
         <v>430</v>
       </c>
       <c r="AR77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AS77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AT77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AU77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -12821,19 +12809,19 @@
         <v>306</v>
       </c>
       <c r="AR78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AS78" t="n">
         <v>0</v>
       </c>
       <c r="AT78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -12979,7 +12967,7 @@
         <v>394</v>
       </c>
       <c r="AR79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AS79" t="n">
         <v>0</v>
@@ -12988,168 +12976,168 @@
         <v>6</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H80" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>40</v>
+      </c>
+      <c r="N80" t="n">
         <v>3</v>
       </c>
-      <c r="I80" t="n">
-        <v>95</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>10</v>
-      </c>
       <c r="O80" t="n">
-        <v>405</v>
+        <v>60</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q80" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S80" t="n">
-        <v>145</v>
+        <v>123.57</v>
       </c>
       <c r="T80" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="U80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AE80" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="AF80" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="AG80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AK80" t="n">
         <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
         <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AQ80" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AR80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AS80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -13295,19 +13283,19 @@
         <v>292</v>
       </c>
       <c r="AR81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AS81" t="n">
         <v>0</v>
       </c>
       <c r="AT81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="n">
         <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -13453,19 +13441,19 @@
         <v>330</v>
       </c>
       <c r="AR82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AS82" t="n">
         <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -13611,19 +13599,19 @@
         <v>299</v>
       </c>
       <c r="AR83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AS83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -13769,19 +13757,19 @@
         <v>316</v>
       </c>
       <c r="AR84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AS84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -13927,19 +13915,19 @@
         <v>299</v>
       </c>
       <c r="AR85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AS85" t="n">
         <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -14085,19 +14073,19 @@
         <v>327</v>
       </c>
       <c r="AR86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AS86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -14243,19 +14231,19 @@
         <v>278</v>
       </c>
       <c r="AR87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AS87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AT87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AU87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AV87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -14401,19 +14389,19 @@
         <v>362</v>
       </c>
       <c r="AR88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AS88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AT88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -14559,19 +14547,19 @@
         <v>333</v>
       </c>
       <c r="AR89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AS89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="n">
         <v>2</v>
       </c>
-      <c r="AU89" t="n">
-        <v>0</v>
-      </c>
       <c r="AV89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -14717,19 +14705,19 @@
         <v>239</v>
       </c>
       <c r="AR90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AS90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="n">
         <v>0</v>
       </c>
       <c r="AV90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -14875,19 +14863,19 @@
         <v>316</v>
       </c>
       <c r="AR91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AS91" t="n">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="n">
         <v>0</v>
       </c>
       <c r="AV91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -15033,19 +15021,19 @@
         <v>360</v>
       </c>
       <c r="AR92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AS92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AU92" t="n">
         <v>0</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -15191,19 +15179,19 @@
         <v>381</v>
       </c>
       <c r="AR93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AS93" t="n">
         <v>0</v>
       </c>
       <c r="AT93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="n">
         <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -15349,10 +15337,10 @@
         <v>278</v>
       </c>
       <c r="AR94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AS94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AT94" t="n">
         <v>4</v>
@@ -15361,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="AV94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -15507,19 +15495,19 @@
         <v>382</v>
       </c>
       <c r="AR95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AS95" t="n">
         <v>0</v>
       </c>
       <c r="AT95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AU95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -15665,19 +15653,19 @@
         <v>366</v>
       </c>
       <c r="AR96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AS96" t="n">
         <v>0</v>
       </c>
       <c r="AT96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AU96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -15823,19 +15811,19 @@
         <v>360</v>
       </c>
       <c r="AR97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AS97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AV97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -15981,19 +15969,19 @@
         <v>248</v>
       </c>
       <c r="AR98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AU98" t="n">
         <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -16139,19 +16127,19 @@
         <v>347</v>
       </c>
       <c r="AR99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AS99" t="n">
         <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -16297,19 +16285,19 @@
         <v>277</v>
       </c>
       <c r="AR100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AS100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -16455,19 +16443,19 @@
         <v>399</v>
       </c>
       <c r="AR101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AS101" t="n">
         <v>0</v>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -16498,7 +16486,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16613,19 +16601,19 @@
         <v>318</v>
       </c>
       <c r="AR102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AS102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AV102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -16771,19 +16759,19 @@
         <v>427</v>
       </c>
       <c r="AR103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AS103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AU103" t="n">
         <v>0</v>
       </c>
       <c r="AV103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -16814,7 +16802,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16929,19 +16917,19 @@
         <v>296</v>
       </c>
       <c r="AR104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AS104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -16976,13 +16964,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I105" t="n">
-        <v>44.45</v>
+        <v>77.78</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -16997,28 +16985,28 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O105" t="n">
-        <v>294.44</v>
+        <v>361.11</v>
       </c>
       <c r="P105" t="n">
         <v>11</v>
       </c>
       <c r="Q105" t="n">
-        <v>180.55</v>
+        <v>247.22</v>
       </c>
       <c r="R105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S105" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="T105" t="n">
         <v>87</v>
       </c>
       <c r="U105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="V105" t="n">
         <v>16</v>
@@ -17039,22 +17027,22 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AE105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AF105" t="n">
         <v>87</v>
       </c>
       <c r="AG105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AH105" t="n">
         <v>16</v>
@@ -17075,31 +17063,31 @@
         <v>0</v>
       </c>
       <c r="AN105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AO105" t="n">
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AQ105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AR105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AS105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -17245,19 +17233,19 @@
         <v>395</v>
       </c>
       <c r="AR106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AS106" t="n">
         <v>1</v>
       </c>
       <c r="AT106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AU106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -17403,19 +17391,19 @@
         <v>307</v>
       </c>
       <c r="AR107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AS107" t="n">
         <v>0</v>
       </c>
       <c r="AT107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU107" t="n">
         <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -17561,19 +17549,19 @@
         <v>368</v>
       </c>
       <c r="AR108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AS108" t="n">
         <v>0</v>
       </c>
       <c r="AT108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -17719,10 +17707,10 @@
         <v>313</v>
       </c>
       <c r="AR109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AS109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
         <v>2</v>
@@ -17731,7 +17719,7 @@
         <v>0</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -17877,10 +17865,10 @@
         <v>404</v>
       </c>
       <c r="AR110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AS110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT110" t="n">
         <v>0</v>
@@ -17889,7 +17877,7 @@
         <v>3</v>
       </c>
       <c r="AV110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -18035,19 +18023,19 @@
         <v>307</v>
       </c>
       <c r="AR111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AS111" t="n">
         <v>0</v>
       </c>
       <c r="AT111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="n">
         <v>0</v>
       </c>
       <c r="AV111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -18193,19 +18181,19 @@
         <v>262</v>
       </c>
       <c r="AR112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -18351,19 +18339,19 @@
         <v>442</v>
       </c>
       <c r="AR113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AS113" t="n">
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AV113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -18509,19 +18497,19 @@
         <v>561</v>
       </c>
       <c r="AR114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AS114" t="n">
         <v>0</v>
       </c>
       <c r="AT114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="n">
         <v>0</v>
       </c>
       <c r="AV114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -18667,19 +18655,19 @@
         <v>271</v>
       </c>
       <c r="AR115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AS115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU115" t="n">
         <v>0</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -18825,60 +18813,60 @@
         <v>292</v>
       </c>
       <c r="AR116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AS116" t="n">
         <v>0</v>
       </c>
       <c r="AT116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H117" t="n">
         <v>3</v>
       </c>
       <c r="I117" t="n">
-        <v>166.66</v>
+        <v>95</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -18896,40 +18884,40 @@
         <v>10</v>
       </c>
       <c r="O117" t="n">
-        <v>350.01</v>
+        <v>405</v>
       </c>
       <c r="P117" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>366.67</v>
+        <v>50</v>
       </c>
       <c r="R117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S117" t="n">
-        <v>533.34</v>
+        <v>145</v>
       </c>
       <c r="T117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="U117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="V117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -18941,31 +18929,31 @@
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AE117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AF117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AG117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="AH117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK117" t="n">
         <v>0</v>
       </c>
       <c r="AL117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM117" t="n">
         <v>0</v>
@@ -18977,66 +18965,66 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AQ117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AR117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AS117" t="n">
         <v>0</v>
       </c>
       <c r="AT117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H118" t="n">
         <v>3</v>
       </c>
       <c r="I118" t="n">
-        <v>72.22</v>
+        <v>166.66</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -19051,31 +19039,31 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>172.22</v>
+        <v>350.01</v>
       </c>
       <c r="P118" t="n">
         <v>7</v>
       </c>
       <c r="Q118" t="n">
-        <v>222.22</v>
+        <v>366.67</v>
       </c>
       <c r="R118" t="n">
         <v>10</v>
       </c>
       <c r="S118" t="n">
-        <v>294.44</v>
+        <v>533.34</v>
       </c>
       <c r="T118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="U118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -19096,22 +19084,22 @@
         <v>42</v>
       </c>
       <c r="AC118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AE118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AF118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="AG118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -19132,108 +19120,108 @@
         <v>42</v>
       </c>
       <c r="AO118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AQ118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AR118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AS118" t="n">
         <v>0</v>
       </c>
       <c r="AT118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU118" t="n">
         <v>0</v>
       </c>
       <c r="AV118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4</v>
+      </c>
+      <c r="O119" t="n">
+        <v>172.22</v>
+      </c>
+      <c r="P119" t="n">
         <v>7</v>
       </c>
-      <c r="I119" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="J119" t="n">
-        <v>5</v>
-      </c>
-      <c r="K119" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="L119" t="n">
-        <v>3</v>
-      </c>
-      <c r="M119" t="n">
+      <c r="Q119" t="n">
+        <v>222.22</v>
+      </c>
+      <c r="R119" t="n">
         <v>10</v>
       </c>
-      <c r="N119" t="n">
-        <v>26</v>
-      </c>
-      <c r="O119" t="n">
-        <v>135.38</v>
-      </c>
-      <c r="P119" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="R119" t="n">
-        <v>9</v>
-      </c>
       <c r="S119" t="n">
-        <v>56.41</v>
+        <v>294.44</v>
       </c>
       <c r="T119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="U119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="V119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -19245,31 +19233,31 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AC119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AE119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AF119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="AG119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="AH119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -19281,117 +19269,117 @@
         <v>0</v>
       </c>
       <c r="AL119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM119" t="n">
         <v>0</v>
       </c>
       <c r="AN119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AO119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AQ119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AR119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AS119" t="n">
         <v>0</v>
       </c>
       <c r="AT119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="n">
         <v>0</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="H120" t="n">
+        <v>7</v>
+      </c>
+      <c r="I120" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="J120" t="n">
         <v>5</v>
       </c>
-      <c r="I120" t="n">
-        <v>108.33</v>
-      </c>
-      <c r="J120" t="n">
-        <v>1</v>
-      </c>
       <c r="K120" t="n">
-        <v>25</v>
+        <v>29.75</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N120" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="O120" t="n">
-        <v>160</v>
+        <v>135.38</v>
       </c>
       <c r="P120" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q120" t="n">
-        <v>308.33</v>
+        <v>11.02</v>
       </c>
       <c r="R120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S120" t="n">
-        <v>416.67</v>
+        <v>56.41</v>
       </c>
       <c r="T120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="U120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="V120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W120" t="n">
         <v>0</v>
@@ -19403,31 +19391,31 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC120" t="n">
         <v>3</v>
       </c>
-      <c r="AA120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
       <c r="AD120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AE120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AF120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="AG120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="AH120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
@@ -19439,78 +19427,78 @@
         <v>0</v>
       </c>
       <c r="AL120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AO120" t="n">
         <v>3</v>
       </c>
-      <c r="AM120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AO120" t="n">
-        <v>0</v>
-      </c>
       <c r="AP120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AQ120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AR120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AS120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="n">
         <v>0</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="H121" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="I121" t="n">
-        <v>100.56</v>
+        <v>108.33</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -19528,31 +19516,31 @@
         <v>6</v>
       </c>
       <c r="O121" t="n">
-        <v>94.44</v>
+        <v>160</v>
       </c>
       <c r="P121" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="Q121" t="n">
-        <v>114.29</v>
+        <v>308.33</v>
       </c>
       <c r="R121" t="n">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="S121" t="n">
-        <v>214.85</v>
+        <v>416.67</v>
       </c>
       <c r="T121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="U121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="V121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="W121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -19561,34 +19549,34 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AC121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AE121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AF121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="AG121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="AH121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AI121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ121" t="n">
         <v>0</v>
@@ -19597,121 +19585,121 @@
         <v>0</v>
       </c>
       <c r="AL121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM121" t="n">
         <v>0</v>
       </c>
       <c r="AN121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AO121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AQ121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AR121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AS121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU121" t="n">
         <v>0</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="H122" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I122" t="n">
-        <v>136.63</v>
+        <v>100.56</v>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>18.24</v>
+        <v>25</v>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>18.24</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>123.81</v>
+        <v>94.44</v>
       </c>
       <c r="P122" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="R122" t="n">
+        <v>118</v>
+      </c>
+      <c r="S122" t="n">
+        <v>214.85</v>
+      </c>
+      <c r="T122" t="n">
+        <v>185</v>
+      </c>
+      <c r="U122" t="n">
+        <v>242</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6</v>
+      </c>
+      <c r="W122" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="R122" t="n">
-        <v>18</v>
-      </c>
-      <c r="S122" t="n">
-        <v>142.34</v>
-      </c>
-      <c r="T122" t="n">
-        <v>126</v>
-      </c>
-      <c r="U122" t="n">
-        <v>256</v>
-      </c>
-      <c r="V122" t="n">
-        <v>16</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
       <c r="X122" t="n">
         <v>0</v>
       </c>
@@ -19719,34 +19707,34 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AE122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AF122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="AG122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AH122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ122" t="n">
         <v>0</v>
@@ -19755,216 +19743,216 @@
         <v>0</v>
       </c>
       <c r="AL122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM122" t="n">
         <v>0</v>
       </c>
       <c r="AN122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AO122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AQ122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AR122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AS122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU122" t="n">
         <v>0</v>
       </c>
       <c r="AV122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H123" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I123" t="n">
-        <v>188.2</v>
+        <v>136.63</v>
       </c>
       <c r="J123" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3</v>
+      </c>
+      <c r="M123" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="N123" t="n">
+        <v>8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>123.81</v>
+      </c>
+      <c r="P123" t="n">
         <v>2</v>
       </c>
-      <c r="K123" t="n">
-        <v>26.79</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>10</v>
-      </c>
-      <c r="O123" t="n">
-        <v>151.75</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
       <c r="Q123" t="n">
-        <v>12.5</v>
+        <v>5.71</v>
       </c>
       <c r="R123" t="n">
+        <v>18</v>
+      </c>
+      <c r="S123" t="n">
+        <v>142.34</v>
+      </c>
+      <c r="T123" t="n">
+        <v>126</v>
+      </c>
+      <c r="U123" t="n">
+        <v>256</v>
+      </c>
+      <c r="V123" t="n">
         <v>16</v>
       </c>
-      <c r="S123" t="n">
-        <v>200.7</v>
-      </c>
-      <c r="T123" t="n">
-        <v>97</v>
-      </c>
-      <c r="U123" t="n">
-        <v>338</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
       <c r="W123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AC123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AE123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AF123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="AG123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="AH123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK123" t="n">
         <v>0</v>
       </c>
       <c r="AL123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM123" t="n">
         <v>0</v>
       </c>
       <c r="AN123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AO123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AQ123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AR123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AS123" t="n">
         <v>0</v>
       </c>
       <c r="AT123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU123" t="n">
         <v>0</v>
       </c>
       <c r="AV123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19978,19 +19966,19 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H124" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I124" t="n">
-        <v>63.69</v>
+        <v>218.2</v>
       </c>
       <c r="J124" t="n">
         <v>3</v>
       </c>
       <c r="K124" t="n">
-        <v>14.29</v>
+        <v>33.93</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -19999,37 +19987,37 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O124" t="n">
-        <v>236.31</v>
+        <v>146.04</v>
       </c>
       <c r="P124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q124" t="n">
-        <v>284.52</v>
+        <v>32.5</v>
       </c>
       <c r="R124" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="S124" t="n">
-        <v>348.22</v>
+        <v>250.7</v>
       </c>
       <c r="T124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="U124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -20041,31 +20029,31 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AC124" t="n">
         <v>1</v>
       </c>
       <c r="AD124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AE124" t="n">
         <v>371</v>
       </c>
       <c r="AF124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="AG124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AH124" t="n">
         <v>0</v>
       </c>
       <c r="AI124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK124" t="n">
         <v>0</v>
@@ -20077,114 +20065,114 @@
         <v>0</v>
       </c>
       <c r="AN124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AO124" t="n">
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AQ124" t="n">
         <v>371</v>
       </c>
       <c r="AR124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AS124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AT124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H125" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I125" t="n">
-        <v>158.33</v>
+        <v>63.69</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="L125" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>47.92</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O125" t="n">
-        <v>87.5</v>
+        <v>236.31</v>
       </c>
       <c r="P125" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q125" t="n">
-        <v>35.42</v>
+        <v>284.52</v>
       </c>
       <c r="R125" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S125" t="n">
-        <v>193.75</v>
+        <v>348.22</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="U125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
@@ -20193,114 +20181,114 @@
         <v>0</v>
       </c>
       <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>326</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
         <v>2</v>
       </c>
-      <c r="AA125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC125" t="n">
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AS125" t="n">
         <v>2</v>
       </c>
-      <c r="AD125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>288</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>0</v>
-      </c>
       <c r="AT125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="n">
         <v>0</v>
       </c>
       <c r="AV125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I126" t="n">
-        <v>42.22</v>
+        <v>158.33</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -20309,156 +20297,156 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>47.92</v>
       </c>
       <c r="N126" t="n">
         <v>6</v>
       </c>
       <c r="O126" t="n">
-        <v>155.56</v>
+        <v>87.5</v>
       </c>
       <c r="P126" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q126" t="n">
-        <v>188.06</v>
+        <v>35.42</v>
       </c>
       <c r="R126" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S126" t="n">
-        <v>230.28</v>
+        <v>193.75</v>
       </c>
       <c r="T126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
         <v>2</v>
       </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>1</v>
-      </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AC126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AE126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AF126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
         <v>2</v>
       </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>1</v>
-      </c>
       <c r="AM126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AO126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AQ126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AR126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AS126" t="n">
         <v>0</v>
       </c>
       <c r="AT126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="n">
         <v>0</v>
       </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="H127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
-        <v>59.72</v>
+        <v>42.22</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -20473,195 +20461,195 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O127" t="n">
-        <v>223.33</v>
+        <v>155.56</v>
       </c>
       <c r="P127" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q127" t="n">
-        <v>1050</v>
+        <v>188.06</v>
       </c>
       <c r="R127" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="S127" t="n">
-        <v>1109.72</v>
+        <v>230.28</v>
       </c>
       <c r="T127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="U127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="V127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AE127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AF127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AG127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="AH127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK127" t="n">
         <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AO127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AQ127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AR127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AS127" t="n">
         <v>0</v>
       </c>
       <c r="AT127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="n">
         <v>0</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H128" t="n">
+        <v>5</v>
+      </c>
+      <c r="I128" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
         <v>10</v>
       </c>
-      <c r="I128" t="n">
-        <v>95.22999999999999</v>
-      </c>
-      <c r="J128" t="n">
-        <v>2</v>
-      </c>
-      <c r="K128" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1</v>
-      </c>
-      <c r="M128" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="N128" t="n">
-        <v>18</v>
-      </c>
       <c r="O128" t="n">
-        <v>177.79</v>
+        <v>223.33</v>
       </c>
       <c r="P128" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1050</v>
+      </c>
+      <c r="R128" t="n">
         <v>19</v>
       </c>
-      <c r="Q128" t="n">
-        <v>173.81</v>
-      </c>
-      <c r="R128" t="n">
-        <v>29</v>
-      </c>
       <c r="S128" t="n">
-        <v>269.04</v>
+        <v>1109.72</v>
       </c>
       <c r="T128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="U128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="V128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="X128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -20673,31 +20661,31 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AE128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AF128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="AG128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="AH128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AJ128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK128" t="n">
         <v>0</v>
@@ -20709,118 +20697,118 @@
         <v>0</v>
       </c>
       <c r="AN128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AO128" t="n">
         <v>0</v>
       </c>
       <c r="AP128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AQ128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AR128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AS128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="H129" t="n">
+        <v>10</v>
+      </c>
+      <c r="I129" t="n">
+        <v>95.22999999999999</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N129" t="n">
+        <v>18</v>
+      </c>
+      <c r="O129" t="n">
+        <v>177.79</v>
+      </c>
+      <c r="P129" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>173.81</v>
+      </c>
+      <c r="R129" t="n">
+        <v>29</v>
+      </c>
+      <c r="S129" t="n">
+        <v>269.04</v>
+      </c>
+      <c r="T129" t="n">
+        <v>131</v>
+      </c>
+      <c r="U129" t="n">
+        <v>317</v>
+      </c>
+      <c r="V129" t="n">
         <v>5</v>
       </c>
-      <c r="I129" t="n">
-        <v>69.69</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>7</v>
-      </c>
-      <c r="O129" t="n">
-        <v>203.03</v>
-      </c>
-      <c r="P129" t="n">
+      <c r="W129" t="n">
+        <v>13</v>
+      </c>
+      <c r="X129" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="R129" t="n">
-        <v>7</v>
-      </c>
-      <c r="S129" t="n">
-        <v>87.88</v>
-      </c>
-      <c r="T129" t="n">
-        <v>59</v>
-      </c>
-      <c r="U129" t="n">
-        <v>187</v>
-      </c>
-      <c r="V129" t="n">
-        <v>9</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>3</v>
-      </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
@@ -20831,88 +20819,88 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AC129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AE129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AF129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="AG129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AH129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK129" t="n">
         <v>0</v>
       </c>
       <c r="AL129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM129" t="n">
         <v>0</v>
       </c>
       <c r="AN129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AO129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AQ129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AR129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AS129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -20926,19 +20914,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="H130" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="I130" t="n">
-        <v>113.45</v>
+        <v>69.69</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -20947,37 +20935,37 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
-        <v>184.82</v>
+        <v>203.03</v>
       </c>
       <c r="P130" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q130" t="n">
-        <v>25.57</v>
+        <v>18.18</v>
       </c>
       <c r="R130" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="S130" t="n">
-        <v>139.02</v>
+        <v>87.88</v>
       </c>
       <c r="T130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U130" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="V130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -20989,28 +20977,28 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AC130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AE130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AF130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AG130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="AH130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AI130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AJ130" t="n">
         <v>0</v>
@@ -21019,84 +21007,84 @@
         <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM130" t="n">
         <v>0</v>
       </c>
       <c r="AN130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AO130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AQ130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AR130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AS130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AU130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="H131" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I131" t="n">
-        <v>80</v>
+        <v>113.45</v>
       </c>
       <c r="J131" t="n">
         <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -21105,34 +21093,34 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O131" t="n">
-        <v>140</v>
+        <v>184.82</v>
       </c>
       <c r="P131" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q131" t="n">
-        <v>60</v>
+        <v>25.57</v>
       </c>
       <c r="R131" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="S131" t="n">
-        <v>140</v>
+        <v>139.02</v>
       </c>
       <c r="T131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="U131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="V131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -21147,28 +21135,28 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AE131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AF131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="AG131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="AH131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AI131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AJ131" t="n">
         <v>0</v>
@@ -21183,189 +21171,347 @@
         <v>0</v>
       </c>
       <c r="AN131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AO131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AQ131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AR131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AS131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="n">
         <v>0</v>
       </c>
       <c r="AV131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>yustindurian@gmail.com</t>
+          <t>yudhistiratangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H132" t="n">
         <v>5</v>
       </c>
       <c r="I132" t="n">
+        <v>80</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>10</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>8</v>
+      </c>
+      <c r="O132" t="n">
+        <v>140</v>
+      </c>
+      <c r="P132" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>60</v>
+      </c>
+      <c r="R132" t="n">
+        <v>9</v>
+      </c>
+      <c r="S132" t="n">
+        <v>140</v>
+      </c>
+      <c r="T132" t="n">
+        <v>139</v>
+      </c>
+      <c r="U132" t="n">
+        <v>209</v>
+      </c>
+      <c r="V132" t="n">
+        <v>6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>209</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Yustin Durian</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>yustindurian@gmail.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fiane Greti Mansauda</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>fianemansauda89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(070) TABUKAN TENGAH</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Kharis</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>24</v>
+      </c>
+      <c r="H133" t="n">
+        <v>5</v>
+      </c>
+      <c r="I133" t="n">
         <v>125</v>
       </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1</v>
-      </c>
-      <c r="M132" t="n">
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
         <v>11.11</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>7</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O133" t="n">
         <v>125</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P133" t="n">
         <v>12</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>275</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>17</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>400</v>
       </c>
-      <c r="T132" t="n">
+      <c r="T133" t="n">
         <v>131</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U133" t="n">
         <v>278</v>
       </c>
-      <c r="V132" t="n">
+      <c r="V133" t="n">
         <v>2</v>
       </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
         <v>43</v>
       </c>
-      <c r="AC132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD132" t="n">
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
         <v>456</v>
       </c>
-      <c r="AE132" t="n">
+      <c r="AE133" t="n">
         <v>325</v>
       </c>
-      <c r="AF132" t="n">
+      <c r="AF133" t="n">
         <v>131</v>
       </c>
-      <c r="AG132" t="n">
+      <c r="AG133" t="n">
         <v>278</v>
       </c>
-      <c r="AH132" t="n">
+      <c r="AH133" t="n">
         <v>2</v>
       </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
         <v>43</v>
       </c>
-      <c r="AO132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP132" t="n">
+      <c r="AO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP133" t="n">
         <v>456</v>
       </c>
-      <c r="AQ132" t="n">
+      <c r="AQ133" t="n">
         <v>325</v>
       </c>
-      <c r="AR132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>0</v>
+      <c r="AR133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
